--- a/Download/AI_conference_template.xlsx
+++ b/Download/AI_conference_template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E46BD40-E856-4477-81B6-1C028055BEBF}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{422380E4-6AE6-4E78-9C2A-1ABDFF67336B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" tabRatio="622" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
   <si>
     <t>CCF</t>
   </si>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <t>European Conference on Computer Vision</t>
+  </si>
+  <si>
+    <t>SIGIR</t>
+  </si>
+  <si>
+    <t>International Conference on Research and Development in Information Retrieval</t>
   </si>
 </sst>
 </file>
@@ -561,13 +567,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" customWidth="1"/>
     <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="96" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.453125" style="2" bestFit="1" customWidth="1"/>
@@ -1198,6 +1204,32 @@
       </c>
       <c r="I22" s="2">
         <v>43334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2">
+        <v>43480</v>
+      </c>
+      <c r="I23" s="2">
+        <v>43667</v>
       </c>
     </row>
   </sheetData>
